--- a/real_estate_feedback_forms/049_real_estate_applicant_questionnaire_form--real_estate_feedback_forms.xlsx
+++ b/real_estate_feedback_forms/049_real_estate_applicant_questionnaire_form--real_estate_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'stable'}</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Stable'}</t>
+          <t>Stable</t>
         </is>
       </c>
     </row>
@@ -1182,29 +1182,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'financially_stable'}</t>
+          <t>financially_stable</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Financially_stable'}</t>
+          <t>Financially stable</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>financial_status_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'financially_stable'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Financially_stable'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'employed'}</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Employed'}</t>
+          <t>Self-employed</t>
         </is>
       </c>
     </row>
@@ -1233,29 +1233,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'self-employed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Self-employed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>employment_status_choices</t>
+          <t>property_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'unemployed'}</t>
+          <t>house</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Unemployed'}</t>
+          <t>House</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'house'}</t>
+          <t>apartment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'House'}</t>
+          <t>Apartment</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'apartment'}</t>
+          <t>townhouse</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Apartment'}</t>
+          <t>Townhouse</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'townhouse'}</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Townhouse'}</t>
+          <t>Condo</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>property_type_choices</t>
+          <t>desired_location_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'condo'}</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Condo'}</t>
+          <t>City</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'city'}</t>
+          <t>suburb</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'City'}</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'suburb'}</t>
+          <t>town</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Suburb'}</t>
+          <t>Town</t>
         </is>
       </c>
     </row>
@@ -1369,29 +1369,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'town'}</t>
+          <t>regional</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Town'}</t>
+          <t>Regional</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>desired_location_choices</t>
+          <t>loan_type_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'regional'}</t>
+          <t>variable</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Regional'}</t>
+          <t>Variable</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'variable'}</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Variable'}</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>loan_type_choices</t>
+          <t>self_employed_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'fixed'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Fixed'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1437,29 +1437,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>self_employed_choices</t>
+          <t>employment_status_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'employed'}</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Employed'}</t>
+          <t>Self-employed</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'self-employed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Self-employed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>employment_status_2_choices</t>
+          <t>employment_status_3_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'unemployed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Unemployed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'employed'}</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Employed'}</t>
+          <t>Self-employed</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'self-employed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Self-employed'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>employment_status_3_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'value':_'unemployed'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'value': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
